--- a/cadastros.xlsx
+++ b/cadastros.xlsx
@@ -1,55 +1,456 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://logaslogistica.sharepoint.com/sites/GED_EQUIPE/Documentos Compartilhados/GERAL/07 - Controladoria/2026/controles de medição/app_publicar/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_02883536F707F2E2B540D619D7F1846167B610A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BD3B328-24DA-41A4-B3C7-62B04EA04897}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clientes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Placas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carretas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Clientes" sheetId="1" r:id="rId1"/>
+    <sheet name="Placas" sheetId="2" r:id="rId2"/>
+    <sheet name="Carretas" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>SERGAS MARATA</t>
+  </si>
+  <si>
+    <t>CBCC</t>
+  </si>
+  <si>
+    <t>ALSCO</t>
+  </si>
+  <si>
+    <t>ALTEC</t>
+  </si>
+  <si>
+    <t>CIAMA</t>
+  </si>
+  <si>
+    <t>SADA</t>
+  </si>
+  <si>
+    <t>SIDERURGICA ITABIRITO</t>
+  </si>
+  <si>
+    <t>SOLIAL ALUMINIO</t>
+  </si>
+  <si>
+    <t>TEAR</t>
+  </si>
+  <si>
+    <t>TEXFUND</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA DAMIÃO</t>
+  </si>
+  <si>
+    <t>POSTO TROPICAL</t>
+  </si>
+  <si>
+    <t>ACQUION</t>
+  </si>
+  <si>
+    <t>BAUDUCCO</t>
+  </si>
+  <si>
+    <t>POUSO ALEGRE</t>
+  </si>
+  <si>
+    <t>COLATINA</t>
+  </si>
+  <si>
+    <t>GUARAPARI</t>
+  </si>
+  <si>
+    <t>POSTO SPINASSE</t>
+  </si>
+  <si>
+    <t>FAZENDA CHAPADÃO</t>
+  </si>
+  <si>
+    <t>AMG ESPODUMENEO</t>
+  </si>
+  <si>
+    <t>LEOPOLDINA</t>
+  </si>
+  <si>
+    <t>PIRAUBA</t>
+  </si>
+  <si>
+    <t>UBA</t>
+  </si>
+  <si>
+    <t>BELGO</t>
+  </si>
+  <si>
+    <t>FORTLEV</t>
+  </si>
+  <si>
+    <t>GRAAL</t>
+  </si>
+  <si>
+    <t>JARDIM CANADÁ</t>
+  </si>
+  <si>
+    <t>METAIS PEQUI</t>
+  </si>
+  <si>
+    <t>PAM</t>
+  </si>
+  <si>
+    <t>VILMA</t>
+  </si>
+  <si>
+    <t>FERMAG</t>
+  </si>
+  <si>
+    <t>P. PLANALTO II</t>
+  </si>
+  <si>
+    <t>POSTO BARRIGÃO</t>
+  </si>
+  <si>
+    <t>POSTO BALANÇA</t>
+  </si>
+  <si>
+    <t>ORLANDIA</t>
+  </si>
+  <si>
+    <t>DOURADOS</t>
+  </si>
+  <si>
+    <t>Placa</t>
+  </si>
+  <si>
+    <t>Carreta</t>
+  </si>
+  <si>
+    <t>OWM 6A89</t>
+  </si>
+  <si>
+    <t>OWM 6D19</t>
+  </si>
+  <si>
+    <t>OWQ 7B04</t>
+  </si>
+  <si>
+    <t>OWR 3E30</t>
+  </si>
+  <si>
+    <t>QUO 3G44</t>
+  </si>
+  <si>
+    <t>QUY 4E23</t>
+  </si>
+  <si>
+    <t>QWT 2A87</t>
+  </si>
+  <si>
+    <t>RUP 3J42</t>
+  </si>
+  <si>
+    <t>TEH 3C06</t>
+  </si>
+  <si>
+    <t>TEH 3C09</t>
+  </si>
+  <si>
+    <t>TDO 0E11</t>
+  </si>
+  <si>
+    <t>TOM 7C63</t>
+  </si>
+  <si>
+    <t>TZG 3J20</t>
+  </si>
+  <si>
+    <t>TZH 3G34</t>
+  </si>
+  <si>
+    <t>TZH 3G92</t>
+  </si>
+  <si>
+    <t>VOLVO</t>
+  </si>
+  <si>
+    <t>FH 460</t>
+  </si>
+  <si>
+    <t>FH 540</t>
+  </si>
+  <si>
+    <t>SCANIA</t>
+  </si>
+  <si>
+    <t>G 410</t>
+  </si>
+  <si>
+    <t>JAC</t>
+  </si>
+  <si>
+    <t>560 CV</t>
+  </si>
+  <si>
+    <t>G 460</t>
+  </si>
+  <si>
+    <t>LRM 1004</t>
+  </si>
+  <si>
+    <t>LVB 1862</t>
+  </si>
+  <si>
+    <t>LUY 1F72</t>
+  </si>
+  <si>
+    <t>LUV 1G81</t>
+  </si>
+  <si>
+    <t>KZS 5277</t>
+  </si>
+  <si>
+    <t>DKA 9412</t>
+  </si>
+  <si>
+    <t>OPQ 3A71</t>
+  </si>
+  <si>
+    <t>OPQ 3A64</t>
+  </si>
+  <si>
+    <t>OQB 9G66</t>
+  </si>
+  <si>
+    <t>DFY 4D45</t>
+  </si>
+  <si>
+    <t>DFY 4D59</t>
+  </si>
+  <si>
+    <t>KVS 1F91</t>
+  </si>
+  <si>
+    <t>KUY 9C75</t>
+  </si>
+  <si>
+    <t>LOZ 1i69</t>
+  </si>
+  <si>
+    <t>LML 7792</t>
+  </si>
+  <si>
+    <t>KRY 6397</t>
+  </si>
+  <si>
+    <t>KWZ9106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BXJ 2J12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BWN 2F71 </t>
+  </si>
+  <si>
+    <t>QUG 3i52</t>
+  </si>
+  <si>
+    <t>QUG 3854</t>
+  </si>
+  <si>
+    <t>CZB 1G38</t>
+  </si>
+  <si>
+    <t>KNT 1B66</t>
+  </si>
+  <si>
+    <t>QXI 7592</t>
+  </si>
+  <si>
+    <t>RMM 2H76</t>
+  </si>
+  <si>
+    <t>RKT 4E97</t>
+  </si>
+  <si>
+    <t>RKJ 4J52</t>
+  </si>
+  <si>
+    <t>RTZ 7H51</t>
+  </si>
+  <si>
+    <t>RTZ 7H56</t>
+  </si>
+  <si>
+    <t>RJE 4F94</t>
+  </si>
+  <si>
+    <t>SHE 5E28</t>
+  </si>
+  <si>
+    <t>SHE 5E29</t>
+  </si>
+  <si>
+    <t>SHM 9A66</t>
+  </si>
+  <si>
+    <t>SHM 9B02</t>
+  </si>
+  <si>
+    <t>SHM 9A84</t>
+  </si>
+  <si>
+    <t>SHM 9A74</t>
+  </si>
+  <si>
+    <t>SIE 5G90</t>
+  </si>
+  <si>
+    <t>RJH 8H42</t>
+  </si>
+  <si>
+    <t>RJH 8H43</t>
+  </si>
+  <si>
+    <t>RJH 8H44</t>
+  </si>
+  <si>
+    <t>RJH 8H45</t>
+  </si>
+  <si>
+    <t>RJH 8H46</t>
+  </si>
+  <si>
+    <t>RJH 8H47</t>
+  </si>
+  <si>
+    <t>SYY3J85</t>
+  </si>
+  <si>
+    <t>SYX-8G40</t>
+  </si>
+  <si>
+    <t>SYX8F99</t>
+  </si>
+  <si>
+    <t>TCC-5H16</t>
+  </si>
+  <si>
+    <t>TCC-5J68</t>
+  </si>
+  <si>
+    <t>TCC-5H25</t>
+  </si>
+  <si>
+    <t>TXZ-1C74</t>
+  </si>
+  <si>
+    <t>TXZ-1C76</t>
+  </si>
+  <si>
+    <t>TYB-9G87</t>
+  </si>
+  <si>
+    <t>TYB-9H23</t>
+  </si>
+  <si>
+    <t>TYD-5H67</t>
+  </si>
+  <si>
+    <t>TYD-2E38</t>
+  </si>
+  <si>
+    <t>TZF-1I69</t>
+  </si>
+  <si>
+    <t>TZF-3I15</t>
+  </si>
+  <si>
+    <t>TZF-7A99</t>
+  </si>
+  <si>
+    <t>TZH-9B59</t>
+  </si>
+  <si>
+    <t>TZH-9B48</t>
+  </si>
+  <si>
+    <t>TZI-5F02</t>
+  </si>
+  <si>
+    <t>TZM-1D30</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5496"/>
+        <fgColor rgb="FF2E5496"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -57,87 +458,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -425,274 +824,196 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SERGAS MARATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CBCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ALSCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ALTEC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CIAMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SIDERURGICA ITABIRITO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SOLIAL ALUMINIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TEXFUND</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRANSPORTADORA DAMIÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>POSTO TROPICAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>ACQUION</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>BAUDUCCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>POUSO ALEGRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>COLATINA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>GUARAPARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>POSTO SPINASSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FAZENDA CHAPADÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>AMG ESPODUMENEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>LEOPOLDINA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>PIRAUBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>UBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>BELGO</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>FORTLEV</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>GRAAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>JARDIM CANADÁ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>METAIS PEQUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>PAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>VILMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>FERMAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>P. PLANALTO II</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>POSTO BARRIGÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>POSTO BALANÇA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>ORLANDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>DOURADOS</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -701,29 +1022,366 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Placa</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>QUO3644</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3">
+        <v>901</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="5">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3">
+        <v>902</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3">
+        <v>903</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3">
+        <v>904</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3">
+        <v>905</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="3">
+        <v>906</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="4">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3">
+        <v>907</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="4">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="3">
+        <v>908</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="4">
+        <v>9</v>
+      </c>
+      <c r="F9" s="4">
+        <v>9</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3">
+        <v>913</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="4">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="3">
+        <v>914</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="4">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="3">
+        <v>915</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4">
+        <v>10</v>
+      </c>
+      <c r="F12" s="4">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3">
+        <v>916</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="3">
+        <v>917</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="4">
+        <v>16</v>
+      </c>
+      <c r="F14" s="4">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="3">
+        <v>918</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="4">
+        <v>15</v>
+      </c>
+      <c r="F15" s="4">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="6">
+        <v>919</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="7">
+        <v>13</v>
+      </c>
+      <c r="F16" s="7">
+        <v>13</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -732,30 +1390,711 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Carreta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="8">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="8">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="8">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="8">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="8">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="8">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="8">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="8">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="8">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="8">
+        <v>12</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="8">
+        <v>13</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="8">
+        <v>14</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="8">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="8">
+        <v>16</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="8">
+        <v>17</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="8">
+        <v>18</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="8">
+        <v>19</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="8">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="8">
+        <v>21</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="8">
+        <v>22</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="8">
+        <v>23</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="8">
+        <v>24</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="8">
+        <v>25</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="8">
+        <v>26</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="8">
+        <v>27</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="8">
+        <v>28</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="8">
+        <v>29</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="8">
+        <v>30</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="8">
+        <v>31</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="8">
+        <v>32</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="8">
+        <v>33</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="8">
+        <v>34</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="8">
+        <v>35</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="8">
+        <v>36</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="8">
+        <v>37</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="8">
+        <v>38</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="8">
+        <v>39</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="8">
+        <v>40</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="8">
+        <v>41</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="8">
+        <v>42</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="8">
+        <v>43</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="8">
+        <v>44</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="8">
+        <v>45</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="8">
+        <v>46</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="8">
+        <v>47</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="8">
+        <v>48</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="8">
+        <v>49</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="8">
+        <v>50</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="8">
+        <v>51</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="8">
+        <v>52</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="8">
+        <v>53</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="8">
+        <v>54</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="8">
+        <v>55</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="8">
+        <v>56</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="8">
+        <v>57</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="8">
+        <v>58</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="8">
+        <v>59</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="8">
+        <v>60</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="8">
+        <v>61</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="8">
+        <v>62</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C64" s="8">
+        <v>63</v>
+      </c>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D65" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -976,15 +2315,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="9f3d96ca-58c5-4b51-bec2-d119553ccef8" xsi:nil="true"/>
@@ -995,14 +2325,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB5A046-F207-401A-9A61-38C93319F469}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB5A046-F207-401A-9A61-38C93319F469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
+    <ds:schemaRef ds:uri="9f3d96ca-58c5-4b51-bec2-d119553ccef8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABCD99-9F57-4CA4-85B4-AA570BB911FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33E031D7-1D53-4C67-AA2C-2F4C96429F5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9f3d96ca-58c5-4b51-bec2-d119553ccef8"/>
+    <ds:schemaRef ds:uri="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33E031D7-1D53-4C67-AA2C-2F4C96429F5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABCD99-9F57-4CA4-85B4-AA570BB911FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/cadastros.xlsx
+++ b/cadastros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://logaslogistica.sharepoint.com/sites/GED_EQUIPE/Documentos Compartilhados/GERAL/07 - Controladoria/2026/controles de medição/app_publicar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_02883536F707F2E2B540D619D7F1846167B610A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BD3B328-24DA-41A4-B3C7-62B04EA04897}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_02883536F707F2E2B540D619D7F1846167B610A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554BAE4C-22D1-4B13-99EF-04DF6DA99FBE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="23280" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="125">
   <si>
     <t>Cliente</t>
   </si>
@@ -1023,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1034,14 +1034,15 @@
     <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>39</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="str">
+        <f>J2</f>
+        <v>901 - OWM 6A89</v>
       </c>
       <c r="C2" s="3">
         <v>901</v>
@@ -1061,10 +1062,15 @@
       <c r="H2" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>40</v>
+      <c r="J2" t="str">
+        <f>_xlfn.CONCAT(C2," - ",D2)</f>
+        <v>901 - OWM 6A89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="str">
+        <f t="shared" ref="A3:A16" si="0">J3</f>
+        <v>902 - OWM 6D19</v>
       </c>
       <c r="C3" s="3">
         <v>902</v>
@@ -1084,10 +1090,15 @@
       <c r="H3" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>41</v>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J16" si="1">_xlfn.CONCAT(C3," - ",D3)</f>
+        <v>902 - OWM 6D19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>903 - OWQ 7B04</v>
       </c>
       <c r="C4" s="3">
         <v>903</v>
@@ -1107,10 +1118,15 @@
       <c r="H4" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>42</v>
+      <c r="J4" t="str">
+        <f t="shared" si="1"/>
+        <v>903 - OWQ 7B04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>904 - OWR 3E30</v>
       </c>
       <c r="C5" s="3">
         <v>904</v>
@@ -1130,10 +1146,15 @@
       <c r="H5" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>43</v>
+      <c r="J5" t="str">
+        <f t="shared" si="1"/>
+        <v>904 - OWR 3E30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>905 - QUO 3G44</v>
       </c>
       <c r="C6" s="3">
         <v>905</v>
@@ -1153,10 +1174,15 @@
       <c r="H6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
+      <c r="J6" t="str">
+        <f t="shared" si="1"/>
+        <v>905 - QUO 3G44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>906 - QUY 4E23</v>
       </c>
       <c r="C7" s="3">
         <v>906</v>
@@ -1176,10 +1202,15 @@
       <c r="H7" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>45</v>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>906 - QUY 4E23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>907 - QWT 2A87</v>
       </c>
       <c r="C8" s="3">
         <v>907</v>
@@ -1199,10 +1230,15 @@
       <c r="H8" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>46</v>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v>907 - QWT 2A87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>908 - RUP 3J42</v>
       </c>
       <c r="C9" s="3">
         <v>908</v>
@@ -1222,10 +1258,15 @@
       <c r="H9" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>47</v>
+      <c r="J9" t="str">
+        <f t="shared" si="1"/>
+        <v>908 - RUP 3J42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>913 - TEH 3C06</v>
       </c>
       <c r="C10" s="3">
         <v>913</v>
@@ -1245,10 +1286,15 @@
       <c r="H10" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>48</v>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>913 - TEH 3C06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>914 - TEH 3C09</v>
       </c>
       <c r="C11" s="3">
         <v>914</v>
@@ -1268,10 +1314,15 @@
       <c r="H11" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
+      <c r="J11" t="str">
+        <f t="shared" si="1"/>
+        <v>914 - TEH 3C09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>915 - TDO 0E11</v>
       </c>
       <c r="C12" s="3">
         <v>915</v>
@@ -1291,10 +1342,15 @@
       <c r="H12" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>50</v>
+      <c r="J12" t="str">
+        <f t="shared" si="1"/>
+        <v>915 - TDO 0E11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>916 - TOM 7C63</v>
       </c>
       <c r="C13" s="3">
         <v>916</v>
@@ -1314,10 +1370,15 @@
       <c r="H13" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>51</v>
+      <c r="J13" t="str">
+        <f t="shared" si="1"/>
+        <v>916 - TOM 7C63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>917 - TZG 3J20</v>
       </c>
       <c r="C14" s="3">
         <v>917</v>
@@ -1337,10 +1398,15 @@
       <c r="H14" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>52</v>
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>917 - TZG 3J20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>918 - TZH 3G34</v>
       </c>
       <c r="C15" s="3">
         <v>918</v>
@@ -1360,10 +1426,15 @@
       <c r="H15" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>53</v>
+      <c r="J15" t="str">
+        <f t="shared" si="1"/>
+        <v>918 - TZH 3G34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>919 - TZH 3G92</v>
       </c>
       <c r="C16" s="6">
         <v>919</v>
@@ -1382,6 +1453,10 @@
       </c>
       <c r="H16" s="7" t="s">
         <v>60</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="1"/>
+        <v>919 - TZH 3G92</v>
       </c>
     </row>
   </sheetData>
@@ -1391,20 +1466,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>62</v>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="str">
+        <f>E2</f>
+        <v>1 - LRM 1004</v>
       </c>
       <c r="C2" s="8">
         <v>1</v>
@@ -1412,10 +1489,15 @@
       <c r="D2" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
+      <c r="E2" t="str">
+        <f>_xlfn.CONCAT(C2," - ",D2)</f>
+        <v>1 - LRM 1004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="str">
+        <f t="shared" ref="A3:A63" si="0">E3</f>
+        <v>2 - LVB 1862</v>
       </c>
       <c r="C3" s="8">
         <v>2</v>
@@ -1423,10 +1505,15 @@
       <c r="D3" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E65" si="1">_xlfn.CONCAT(C3," - ",D3)</f>
+        <v>2 - LVB 1862</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>3 - LUY 1F72</v>
       </c>
       <c r="C4" s="8">
         <v>3</v>
@@ -1434,10 +1521,15 @@
       <c r="D4" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
+      <c r="E4" t="str">
+        <f t="shared" si="1"/>
+        <v>3 - LUY 1F72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>4 - LUV 1G81</v>
       </c>
       <c r="C5" s="8">
         <v>4</v>
@@ -1445,10 +1537,15 @@
       <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
+      <c r="E5" t="str">
+        <f t="shared" si="1"/>
+        <v>4 - LUV 1G81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>5 - KZS 5277</v>
       </c>
       <c r="C6" s="8">
         <v>5</v>
@@ -1456,10 +1553,15 @@
       <c r="D6" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
+      <c r="E6" t="str">
+        <f t="shared" si="1"/>
+        <v>5 - KZS 5277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>6 - DKA 9412</v>
       </c>
       <c r="C7" s="8">
         <v>6</v>
@@ -1467,10 +1569,15 @@
       <c r="D7" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
+      <c r="E7" t="str">
+        <f t="shared" si="1"/>
+        <v>6 - DKA 9412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>7 - OPQ 3A71</v>
       </c>
       <c r="C8" s="8">
         <v>7</v>
@@ -1478,10 +1585,15 @@
       <c r="D8" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
+      <c r="E8" t="str">
+        <f t="shared" si="1"/>
+        <v>7 - OPQ 3A71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>8 - OPQ 3A64</v>
       </c>
       <c r="C9" s="8">
         <v>8</v>
@@ -1489,10 +1601,15 @@
       <c r="D9" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
+      <c r="E9" t="str">
+        <f t="shared" si="1"/>
+        <v>8 - OPQ 3A64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>9 - OQB 9G66</v>
       </c>
       <c r="C10" s="8">
         <v>9</v>
@@ -1500,10 +1617,15 @@
       <c r="D10" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
+      <c r="E10" t="str">
+        <f t="shared" si="1"/>
+        <v>9 - OQB 9G66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>10 - DFY 4D45</v>
       </c>
       <c r="C11" s="8">
         <v>10</v>
@@ -1511,10 +1633,15 @@
       <c r="D11" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
+      <c r="E11" t="str">
+        <f t="shared" si="1"/>
+        <v>10 - DFY 4D45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>11 - DFY 4D59</v>
       </c>
       <c r="C12" s="8">
         <v>11</v>
@@ -1522,10 +1649,15 @@
       <c r="D12" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
+      <c r="E12" t="str">
+        <f t="shared" si="1"/>
+        <v>11 - DFY 4D59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>12 - KVS 1F91</v>
       </c>
       <c r="C13" s="8">
         <v>12</v>
@@ -1533,10 +1665,15 @@
       <c r="D13" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
+      <c r="E13" t="str">
+        <f t="shared" si="1"/>
+        <v>12 - KVS 1F91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>13 - KUY 9C75</v>
       </c>
       <c r="C14" s="8">
         <v>13</v>
@@ -1544,10 +1681,15 @@
       <c r="D14" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
+      <c r="E14" t="str">
+        <f t="shared" si="1"/>
+        <v>13 - KUY 9C75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>14 - LOZ 1i69</v>
       </c>
       <c r="C15" s="8">
         <v>14</v>
@@ -1555,10 +1697,15 @@
       <c r="D15" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
+      <c r="E15" t="str">
+        <f t="shared" si="1"/>
+        <v>14 - LOZ 1i69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>15 - LML 7792</v>
       </c>
       <c r="C16" s="8">
         <v>15</v>
@@ -1566,10 +1713,15 @@
       <c r="D16" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>77</v>
+      <c r="E16" t="str">
+        <f t="shared" si="1"/>
+        <v>15 - LML 7792</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>16 - KRY 6397</v>
       </c>
       <c r="C17" s="8">
         <v>16</v>
@@ -1577,10 +1729,15 @@
       <c r="D17" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>78</v>
+      <c r="E17" t="str">
+        <f t="shared" si="1"/>
+        <v>16 - KRY 6397</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>17 - KWZ9106</v>
       </c>
       <c r="C18" s="8">
         <v>17</v>
@@ -1588,10 +1745,15 @@
       <c r="D18" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>79</v>
+      <c r="E18" t="str">
+        <f t="shared" si="1"/>
+        <v>17 - KWZ9106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">18 - BXJ 2J12 </v>
       </c>
       <c r="C19" s="8">
         <v>18</v>
@@ -1599,10 +1761,15 @@
       <c r="D19" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>80</v>
+      <c r="E19" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">18 - BXJ 2J12 </v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">19 - BWN 2F71 </v>
       </c>
       <c r="C20" s="8">
         <v>19</v>
@@ -1610,10 +1777,15 @@
       <c r="D20" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>81</v>
+      <c r="E20" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">19 - BWN 2F71 </v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>20 - QUG 3i52</v>
       </c>
       <c r="C21" s="8">
         <v>20</v>
@@ -1621,10 +1793,15 @@
       <c r="D21" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>82</v>
+      <c r="E21" t="str">
+        <f t="shared" si="1"/>
+        <v>20 - QUG 3i52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>21 - QUG 3854</v>
       </c>
       <c r="C22" s="8">
         <v>21</v>
@@ -1632,10 +1809,15 @@
       <c r="D22" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>83</v>
+      <c r="E22" t="str">
+        <f t="shared" si="1"/>
+        <v>21 - QUG 3854</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>22 - CZB 1G38</v>
       </c>
       <c r="C23" s="8">
         <v>22</v>
@@ -1643,10 +1825,15 @@
       <c r="D23" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>84</v>
+      <c r="E23" t="str">
+        <f t="shared" si="1"/>
+        <v>22 - CZB 1G38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>23 - KNT 1B66</v>
       </c>
       <c r="C24" s="8">
         <v>23</v>
@@ -1654,10 +1841,15 @@
       <c r="D24" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>85</v>
+      <c r="E24" t="str">
+        <f t="shared" si="1"/>
+        <v>23 - KNT 1B66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>24 - QXI 7592</v>
       </c>
       <c r="C25" s="8">
         <v>24</v>
@@ -1665,10 +1857,15 @@
       <c r="D25" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>86</v>
+      <c r="E25" t="str">
+        <f t="shared" si="1"/>
+        <v>24 - QXI 7592</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>25 - RMM 2H76</v>
       </c>
       <c r="C26" s="8">
         <v>25</v>
@@ -1676,10 +1873,15 @@
       <c r="D26" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>87</v>
+      <c r="E26" t="str">
+        <f t="shared" si="1"/>
+        <v>25 - RMM 2H76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>26 - RKT 4E97</v>
       </c>
       <c r="C27" s="8">
         <v>26</v>
@@ -1687,10 +1889,15 @@
       <c r="D27" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>88</v>
+      <c r="E27" t="str">
+        <f t="shared" si="1"/>
+        <v>26 - RKT 4E97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>27 - RKJ 4J52</v>
       </c>
       <c r="C28" s="8">
         <v>27</v>
@@ -1698,10 +1905,15 @@
       <c r="D28" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>89</v>
+      <c r="E28" t="str">
+        <f t="shared" si="1"/>
+        <v>27 - RKJ 4J52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>28 - RTZ 7H51</v>
       </c>
       <c r="C29" s="8">
         <v>28</v>
@@ -1709,10 +1921,15 @@
       <c r="D29" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>90</v>
+      <c r="E29" t="str">
+        <f t="shared" si="1"/>
+        <v>28 - RTZ 7H51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>29 - RTZ 7H56</v>
       </c>
       <c r="C30" s="8">
         <v>29</v>
@@ -1720,10 +1937,15 @@
       <c r="D30" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>91</v>
+      <c r="E30" t="str">
+        <f t="shared" si="1"/>
+        <v>29 - RTZ 7H56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>30 - RJE 4F94</v>
       </c>
       <c r="C31" s="8">
         <v>30</v>
@@ -1731,10 +1953,15 @@
       <c r="D31" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>92</v>
+      <c r="E31" t="str">
+        <f t="shared" si="1"/>
+        <v>30 - RJE 4F94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>31 - SHE 5E28</v>
       </c>
       <c r="C32" s="8">
         <v>31</v>
@@ -1742,10 +1969,15 @@
       <c r="D32" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>93</v>
+      <c r="E32" t="str">
+        <f t="shared" si="1"/>
+        <v>31 - SHE 5E28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>32 - SHE 5E29</v>
       </c>
       <c r="C33" s="8">
         <v>32</v>
@@ -1753,10 +1985,15 @@
       <c r="D33" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>94</v>
+      <c r="E33" t="str">
+        <f t="shared" si="1"/>
+        <v>32 - SHE 5E29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>33 - SHM 9A66</v>
       </c>
       <c r="C34" s="8">
         <v>33</v>
@@ -1764,10 +2001,15 @@
       <c r="D34" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>95</v>
+      <c r="E34" t="str">
+        <f t="shared" si="1"/>
+        <v>33 - SHM 9A66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>34 - SHM 9B02</v>
       </c>
       <c r="C35" s="8">
         <v>34</v>
@@ -1775,10 +2017,15 @@
       <c r="D35" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>96</v>
+      <c r="E35" t="str">
+        <f t="shared" si="1"/>
+        <v>34 - SHM 9B02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>35 - SHM 9A84</v>
       </c>
       <c r="C36" s="8">
         <v>35</v>
@@ -1786,10 +2033,15 @@
       <c r="D36" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>97</v>
+      <c r="E36" t="str">
+        <f t="shared" si="1"/>
+        <v>35 - SHM 9A84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>36 - SHM 9A74</v>
       </c>
       <c r="C37" s="8">
         <v>36</v>
@@ -1797,10 +2049,15 @@
       <c r="D37" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>98</v>
+      <c r="E37" t="str">
+        <f t="shared" si="1"/>
+        <v>36 - SHM 9A74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>37 - SIE 5G90</v>
       </c>
       <c r="C38" s="8">
         <v>37</v>
@@ -1808,10 +2065,15 @@
       <c r="D38" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>99</v>
+      <c r="E38" t="str">
+        <f t="shared" si="1"/>
+        <v>37 - SIE 5G90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>38 - RJH 8H42</v>
       </c>
       <c r="C39" s="8">
         <v>38</v>
@@ -1819,10 +2081,15 @@
       <c r="D39" s="4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>100</v>
+      <c r="E39" t="str">
+        <f t="shared" si="1"/>
+        <v>38 - RJH 8H42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>39 - RJH 8H43</v>
       </c>
       <c r="C40" s="8">
         <v>39</v>
@@ -1830,10 +2097,15 @@
       <c r="D40" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>101</v>
+      <c r="E40" t="str">
+        <f t="shared" si="1"/>
+        <v>39 - RJH 8H43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>40 - RJH 8H44</v>
       </c>
       <c r="C41" s="8">
         <v>40</v>
@@ -1841,10 +2113,15 @@
       <c r="D41" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>102</v>
+      <c r="E41" t="str">
+        <f t="shared" si="1"/>
+        <v>40 - RJH 8H44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>41 - RJH 8H45</v>
       </c>
       <c r="C42" s="8">
         <v>41</v>
@@ -1852,10 +2129,15 @@
       <c r="D42" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>103</v>
+      <c r="E42" t="str">
+        <f t="shared" si="1"/>
+        <v>41 - RJH 8H45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>42 - RJH 8H46</v>
       </c>
       <c r="C43" s="8">
         <v>42</v>
@@ -1863,10 +2145,15 @@
       <c r="D43" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>104</v>
+      <c r="E43" t="str">
+        <f t="shared" si="1"/>
+        <v>42 - RJH 8H46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>43 - RJH 8H47</v>
       </c>
       <c r="C44" s="8">
         <v>43</v>
@@ -1874,10 +2161,15 @@
       <c r="D44" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>105</v>
+      <c r="E44" t="str">
+        <f t="shared" si="1"/>
+        <v>43 - RJH 8H47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>44 - SYY3J85</v>
       </c>
       <c r="C45" s="8">
         <v>44</v>
@@ -1885,10 +2177,15 @@
       <c r="D45" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>106</v>
+      <c r="E45" t="str">
+        <f t="shared" si="1"/>
+        <v>44 - SYY3J85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>45 - SYX-8G40</v>
       </c>
       <c r="C46" s="8">
         <v>45</v>
@@ -1896,10 +2193,15 @@
       <c r="D46" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>107</v>
+      <c r="E46" t="str">
+        <f t="shared" si="1"/>
+        <v>45 - SYX-8G40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>46 - SYX8F99</v>
       </c>
       <c r="C47" s="8">
         <v>46</v>
@@ -1907,10 +2209,15 @@
       <c r="D47" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>108</v>
+      <c r="E47" t="str">
+        <f t="shared" si="1"/>
+        <v>46 - SYX8F99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>47 - TCC-5H16</v>
       </c>
       <c r="C48" s="8">
         <v>47</v>
@@ -1918,10 +2225,15 @@
       <c r="D48" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>109</v>
+      <c r="E48" t="str">
+        <f t="shared" si="1"/>
+        <v>47 - TCC-5H16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>48 - TCC-5J68</v>
       </c>
       <c r="C49" s="8">
         <v>48</v>
@@ -1929,10 +2241,15 @@
       <c r="D49" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>110</v>
+      <c r="E49" t="str">
+        <f t="shared" si="1"/>
+        <v>48 - TCC-5J68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>49 - TCC-5H25</v>
       </c>
       <c r="C50" s="8">
         <v>49</v>
@@ -1940,10 +2257,15 @@
       <c r="D50" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>111</v>
+      <c r="E50" t="str">
+        <f t="shared" si="1"/>
+        <v>49 - TCC-5H25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>50 - TXZ-1C74</v>
       </c>
       <c r="C51" s="8">
         <v>50</v>
@@ -1951,10 +2273,15 @@
       <c r="D51" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>112</v>
+      <c r="E51" t="str">
+        <f t="shared" si="1"/>
+        <v>50 - TXZ-1C74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>51 - TXZ-1C76</v>
       </c>
       <c r="C52" s="8">
         <v>51</v>
@@ -1962,10 +2289,15 @@
       <c r="D52" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>113</v>
+      <c r="E52" t="str">
+        <f t="shared" si="1"/>
+        <v>51 - TXZ-1C76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>52 - TYB-9G87</v>
       </c>
       <c r="C53" s="8">
         <v>52</v>
@@ -1973,10 +2305,15 @@
       <c r="D53" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>114</v>
+      <c r="E53" t="str">
+        <f t="shared" si="1"/>
+        <v>52 - TYB-9G87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>53 - TYB-9H23</v>
       </c>
       <c r="C54" s="8">
         <v>53</v>
@@ -1984,10 +2321,15 @@
       <c r="D54" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>115</v>
+      <c r="E54" t="str">
+        <f t="shared" si="1"/>
+        <v>53 - TYB-9H23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>54 - TYD-5H67</v>
       </c>
       <c r="C55" s="8">
         <v>54</v>
@@ -1995,10 +2337,15 @@
       <c r="D55" s="4" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>116</v>
+      <c r="E55" t="str">
+        <f t="shared" si="1"/>
+        <v>54 - TYD-5H67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>55 - TYD-2E38</v>
       </c>
       <c r="C56" s="8">
         <v>55</v>
@@ -2006,10 +2353,15 @@
       <c r="D56" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>117</v>
+      <c r="E56" t="str">
+        <f t="shared" si="1"/>
+        <v>55 - TYD-2E38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>56 - TZF-1I69</v>
       </c>
       <c r="C57" s="8">
         <v>56</v>
@@ -2017,10 +2369,15 @@
       <c r="D57" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>118</v>
+      <c r="E57" t="str">
+        <f t="shared" si="1"/>
+        <v>56 - TZF-1I69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>57 - TZF-3I15</v>
       </c>
       <c r="C58" s="8">
         <v>57</v>
@@ -2028,10 +2385,15 @@
       <c r="D58" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>119</v>
+      <c r="E58" t="str">
+        <f t="shared" si="1"/>
+        <v>57 - TZF-3I15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>58 - TZF-7A99</v>
       </c>
       <c r="C59" s="8">
         <v>58</v>
@@ -2039,10 +2401,15 @@
       <c r="D59" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>120</v>
+      <c r="E59" t="str">
+        <f t="shared" si="1"/>
+        <v>58 - TZF-7A99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>59 - TZH-9B59</v>
       </c>
       <c r="C60" s="8">
         <v>59</v>
@@ -2050,10 +2417,15 @@
       <c r="D60" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>121</v>
+      <c r="E60" t="str">
+        <f t="shared" si="1"/>
+        <v>59 - TZH-9B59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>60 - TZH-9B48</v>
       </c>
       <c r="C61" s="8">
         <v>60</v>
@@ -2061,10 +2433,15 @@
       <c r="D61" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>122</v>
+      <c r="E61" t="str">
+        <f t="shared" si="1"/>
+        <v>60 - TZH-9B48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>61 - TZI-5F02</v>
       </c>
       <c r="C62" s="8">
         <v>61</v>
@@ -2072,10 +2449,15 @@
       <c r="D62" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>123</v>
+      <c r="E62" t="str">
+        <f t="shared" si="1"/>
+        <v>61 - TZI-5F02</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>62 - TZM-1D30</v>
       </c>
       <c r="C63" s="8">
         <v>62</v>
@@ -2083,18 +2465,30 @@
       <c r="D63" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" t="str">
+        <f t="shared" si="1"/>
+        <v>62 - TZM-1D30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C64" s="8">
         <v>63</v>
       </c>
       <c r="D64" s="4"/>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="E64" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">63 - </v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C65" s="9" t="s">
         <v>124</v>
       </c>
       <c r="D65" s="7"/>
+      <c r="E65" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">ES - </v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2102,6 +2496,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9f3d96ca-58c5-4b51-bec2-d119553ccef8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44a8a12c-407d-4198-bc6a-221e722a26ec">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005687CE865E48D74DAA77286B453077D9" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="d2055ca21502b0a75c053a1f3a5c7d08">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44a8a12c-407d-4198-bc6a-221e722a26ec" xmlns:ns3="9f3d96ca-58c5-4b51-bec2-d119553ccef8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="04e87c9d151b00042f87940cb66ba149" ns2:_="" ns3:_="">
     <xsd:import namespace="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
@@ -2314,27 +2728,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9f3d96ca-58c5-4b51-bec2-d119553ccef8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44a8a12c-407d-4198-bc6a-221e722a26ec">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABCD99-9F57-4CA4-85B4-AA570BB911FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33E031D7-1D53-4C67-AA2C-2F4C96429F5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9f3d96ca-58c5-4b51-bec2-d119553ccef8"/>
+    <ds:schemaRef ds:uri="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB5A046-F207-401A-9A61-38C93319F469}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2351,23 +2764,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33E031D7-1D53-4C67-AA2C-2F4C96429F5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9f3d96ca-58c5-4b51-bec2-d119553ccef8"/>
-    <ds:schemaRef ds:uri="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABCD99-9F57-4CA4-85B4-AA570BB911FD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/cadastros.xlsx
+++ b/cadastros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://logaslogistica.sharepoint.com/sites/GED_EQUIPE/Documentos Compartilhados/GERAL/07 - Controladoria/2026/controles de medição/app_publicar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_02883536F707F2E2B540D619D7F1846167B610A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554BAE4C-22D1-4B13-99EF-04DF6DA99FBE}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_02883536F707F2E2B540D619D7F1846167B610A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C3619B4-98C8-4D17-A096-B1EB0145B920}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="23280" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="129">
   <si>
     <t>Cliente</t>
   </si>
@@ -410,13 +410,25 @@
   </si>
   <si>
     <t>ES</t>
+  </si>
+  <si>
+    <t>cont. TLQ 4 I57</t>
+  </si>
+  <si>
+    <t>cont. SWA 4I77</t>
+  </si>
+  <si>
+    <t>cont. FQO 4B75</t>
+  </si>
+  <si>
+    <t>cont. TZJ 2E87</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,6 +447,12 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1023,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1032,6 +1050,7 @@
     <col min="5" max="6" width="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1069,7 +1088,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f t="shared" ref="A3:A16" si="0">J3</f>
+        <f t="shared" ref="A3:A4" si="0">J3</f>
         <v>902 - OWM 6D19</v>
       </c>
       <c r="C3" s="3">
@@ -1091,7 +1110,7 @@
         <v>55</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J16" si="1">_xlfn.CONCAT(C3," - ",D3)</f>
+        <f t="shared" ref="J3:J4" si="1">_xlfn.CONCAT(C3," - ",D3)</f>
         <v>902 - OWM 6D19</v>
       </c>
     </row>
@@ -1124,273 +1143,181 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>904 - OWR 3E30</v>
-      </c>
-      <c r="C5" s="3">
-        <v>904</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="4">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4">
-        <v>5</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="1"/>
-        <v>904 - OWR 3E30</v>
+      <c r="A5" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>905 - QUO 3G44</v>
-      </c>
-      <c r="C6" s="3">
-        <v>905</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="4">
-        <v>6</v>
-      </c>
-      <c r="F6" s="4">
-        <v>6</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="1"/>
-        <v>905 - QUO 3G44</v>
+      <c r="A6" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>906 - QUY 4E23</v>
-      </c>
-      <c r="C7" s="3">
-        <v>906</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="4">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4">
-        <v>7</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="1"/>
-        <v>906 - QUY 4E23</v>
+      <c r="A7" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>907 - QWT 2A87</v>
-      </c>
-      <c r="C8" s="3">
-        <v>907</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="4">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4">
-        <v>8</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="1"/>
-        <v>907 - QWT 2A87</v>
+      <c r="A8" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>908 - RUP 3J42</v>
+        <f>J9</f>
+        <v>904 - OWR 3E30</v>
       </c>
       <c r="C9" s="3">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E9" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="1"/>
-        <v>908 - RUP 3J42</v>
+        <f>_xlfn.CONCAT(C9," - ",D9)</f>
+        <v>904 - OWR 3E30</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>913 - TEH 3C06</v>
+        <f>J10</f>
+        <v>905 - QUO 3G44</v>
       </c>
       <c r="C10" s="3">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="1"/>
-        <v>913 - TEH 3C06</v>
+        <f>_xlfn.CONCAT(C10," - ",D10)</f>
+        <v>905 - QUO 3G44</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>914 - TEH 3C09</v>
+        <f>J11</f>
+        <v>906 - QUY 4E23</v>
       </c>
       <c r="C11" s="3">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F11" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="1"/>
-        <v>914 - TEH 3C09</v>
+        <f>_xlfn.CONCAT(C11," - ",D11)</f>
+        <v>906 - QUY 4E23</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>915 - TDO 0E11</v>
+        <f>J12</f>
+        <v>907 - QWT 2A87</v>
       </c>
       <c r="C12" s="3">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E12" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J12" t="str">
-        <f t="shared" si="1"/>
-        <v>915 - TDO 0E11</v>
+        <f>_xlfn.CONCAT(C12," - ",D12)</f>
+        <v>907 - QWT 2A87</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>916 - TOM 7C63</v>
+        <f>J13</f>
+        <v>908 - RUP 3J42</v>
       </c>
       <c r="C13" s="3">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E13" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F13" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J13" t="str">
-        <f t="shared" si="1"/>
-        <v>916 - TOM 7C63</v>
+        <f>_xlfn.CONCAT(C13," - ",D13)</f>
+        <v>908 - RUP 3J42</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>917 - TZG 3J20</v>
+        <f>J14</f>
+        <v>913 - TEH 3C06</v>
       </c>
       <c r="C14" s="3">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E14" s="4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F14" s="4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>59</v>
@@ -1399,26 +1326,26 @@
         <v>60</v>
       </c>
       <c r="J14" t="str">
-        <f t="shared" si="1"/>
-        <v>917 - TZG 3J20</v>
+        <f>_xlfn.CONCAT(C14," - ",D14)</f>
+        <v>913 - TEH 3C06</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>918 - TZH 3G34</v>
+        <f>J15</f>
+        <v>914 - TEH 3C09</v>
       </c>
       <c r="C15" s="3">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E15" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>59</v>
@@ -1427,39 +1354,161 @@
         <v>60</v>
       </c>
       <c r="J15" t="str">
-        <f t="shared" si="1"/>
-        <v>918 - TZH 3G34</v>
+        <f>_xlfn.CONCAT(C15," - ",D15)</f>
+        <v>914 - TEH 3C09</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>J16</f>
+        <v>915 - TDO 0E11</v>
+      </c>
+      <c r="C16" s="3">
+        <v>915</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="4">
+        <v>10</v>
+      </c>
+      <c r="F16" s="4">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" t="str">
+        <f>_xlfn.CONCAT(C16," - ",D16)</f>
+        <v>915 - TDO 0E11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="str">
+        <f>J17</f>
+        <v>916 - TOM 7C63</v>
+      </c>
+      <c r="C17" s="3">
+        <v>916</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="4">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4">
+        <v>14</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" t="str">
+        <f>_xlfn.CONCAT(C17," - ",D17)</f>
+        <v>916 - TOM 7C63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="str">
+        <f>J18</f>
+        <v>917 - TZG 3J20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>917</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="4">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" t="str">
+        <f>_xlfn.CONCAT(C18," - ",D18)</f>
+        <v>917 - TZG 3J20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="str">
+        <f>J19</f>
+        <v>918 - TZH 3G34</v>
+      </c>
+      <c r="C19" s="3">
+        <v>918</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="4">
+        <v>15</v>
+      </c>
+      <c r="F19" s="4">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" t="str">
+        <f>_xlfn.CONCAT(C19," - ",D19)</f>
+        <v>918 - TZH 3G34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="str">
+        <f>J20</f>
         <v>919 - TZH 3G92</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C20" s="6">
         <v>919</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E20" s="7">
         <v>13</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F20" s="7">
         <v>13</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J16" t="str">
-        <f t="shared" si="1"/>
+      <c r="J20" t="str">
+        <f>_xlfn.CONCAT(C20," - ",D20)</f>
         <v>919 - TZH 3G92</v>
       </c>
     </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2496,26 +2545,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9f3d96ca-58c5-4b51-bec2-d119553ccef8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44a8a12c-407d-4198-bc6a-221e722a26ec">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005687CE865E48D74DAA77286B453077D9" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="d2055ca21502b0a75c053a1f3a5c7d08">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44a8a12c-407d-4198-bc6a-221e722a26ec" xmlns:ns3="9f3d96ca-58c5-4b51-bec2-d119553ccef8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="04e87c9d151b00042f87940cb66ba149" ns2:_="" ns3:_="">
     <xsd:import namespace="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
@@ -2728,10 +2757,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9f3d96ca-58c5-4b51-bec2-d119553ccef8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44a8a12c-407d-4198-bc6a-221e722a26ec">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABCD99-9F57-4CA4-85B4-AA570BB911FD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB5A046-F207-401A-9A61-38C93319F469}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
+    <ds:schemaRef ds:uri="9f3d96ca-58c5-4b51-bec2-d119553ccef8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2748,20 +2808,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB5A046-F207-401A-9A61-38C93319F469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABCD99-9F57-4CA4-85B4-AA570BB911FD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44a8a12c-407d-4198-bc6a-221e722a26ec"/>
-    <ds:schemaRef ds:uri="9f3d96ca-58c5-4b51-bec2-d119553ccef8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>